--- a/registration_forms/036_hospitality_conference_registration_form--registration_forms.xlsx
+++ b/registration_forms/036_hospitality_conference_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'conference',_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'conference', 'label': 'Conference'}</t>
+          <t>Conference</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'workshop',_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'workshop', 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_30,_'name':_'meeting',_'label':_'meeting'}</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 30, 'name': 'meeting', 'label': 'Meeting'}</t>
+          <t>Meeting</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_40,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 40, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_50,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 50, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_60,_'name':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 60, 'name': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_70,_'name':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 70, 'name': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_80,_'name':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 80, 'name': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_90,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 90, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
